--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.8-information-security-in-project-management/WKBK/90_workbooks/ISMS-IMP-A.5.8.1_Project_Lifecycle_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.8-information-security-in-project-management/WKBK/90_workbooks/ISMS-IMP-A.5.8.1_Project_Lifecycle_Assessment_20260208.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>External exposure + PCI DSS + customer PII</t>
+          <t>External exposure + PCI DSS v4.0.1 + customer PII</t>
         </is>
       </c>
     </row>
